--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -1,33 +1,109 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BB1855-5025-4F51-B827-2F52C007050D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30910" yWindow="1670" windowWidth="19200" windowHeight="9960" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rientri" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rientri" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+  <si>
+    <t>Codice consegna</t>
+  </si>
+  <si>
+    <t>Data DDT</t>
+  </si>
+  <si>
+    <t>Stato</t>
+  </si>
+  <si>
+    <t>p1791</t>
+  </si>
+  <si>
+    <t>Allegato con DDT (12/03/2026)</t>
+  </si>
+  <si>
+    <t>p2114</t>
+  </si>
+  <si>
+    <t>p14089</t>
+  </si>
+  <si>
+    <t>p2654</t>
+  </si>
+  <si>
+    <t>p1704</t>
+  </si>
+  <si>
+    <t>p1794</t>
+  </si>
+  <si>
+    <t>p1792</t>
+  </si>
+  <si>
+    <t>p2090</t>
+  </si>
+  <si>
+    <t>p2091</t>
+  </si>
+  <si>
+    <t>Allegato con DDT (17/03/2026)</t>
+  </si>
+  <si>
+    <t>p2383</t>
+  </si>
+  <si>
+    <t>Allegato con DDT (18/03/2026)</t>
+  </si>
+  <si>
+    <t>p1789</t>
+  </si>
+  <si>
+    <t>p2339</t>
+  </si>
+  <si>
+    <t>p1994</t>
+  </si>
+  <si>
+    <t>p2381</t>
+  </si>
+  <si>
+    <t>p2673</t>
+  </si>
+  <si>
+    <t>p2023</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +122,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,171 +425,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="20.81640625" defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="20.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="13.36328125" customWidth="1" style="1" min="2" max="2"/>
+    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Codice consegna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Data DDT</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>p1791</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>p2114</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>p14089</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>p2654</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>p1704</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>p1794</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>p1792</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>05-03-2026</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Allegato con DDT (12/03/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>p2090</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
         <v>46091</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>p2091</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="n">
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1">
         <v>46091</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46093</v>
       </c>
     </row>
   </sheetData>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BB1855-5025-4F51-B827-2F52C007050D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D660E22D-97DE-4C58-9AF6-05E82227F581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
   <si>
     <t>Codice consegna</t>
   </si>
@@ -86,6 +86,9 @@
   </si>
   <si>
     <t>p2023</t>
+  </si>
+  <si>
+    <t>Allegato con DDT (19/03/2026)</t>
   </si>
 </sst>
 </file>
@@ -426,13 +429,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="20.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,7 +446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -454,7 +457,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -465,7 +468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -476,7 +479,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -487,7 +490,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -498,7 +501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -509,7 +512,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -520,7 +523,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -531,7 +534,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -542,7 +545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -553,23 +556,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="1">
         <v>46093</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -580,7 +589,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -591,7 +600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -599,7 +608,7 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -607,12 +616,15 @@
         <v>46097</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>46093</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D660E22D-97DE-4C58-9AF6-05E82227F581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7071F3BD-5D4A-4DE6-9833-8CF5A3F904A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="25">
   <si>
     <t>Codice consegna</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Allegato con DDT (19/03/2026)</t>
+  </si>
+  <si>
+    <t>p2359</t>
+  </si>
+  <si>
+    <t>p1874</t>
   </si>
 </sst>
 </file>
@@ -429,13 +435,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="20.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,7 +452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -457,7 +463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -468,7 +474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -479,7 +485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -490,7 +496,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -501,7 +507,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -512,7 +518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -523,7 +529,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -534,7 +540,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -545,7 +551,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -556,29 +562,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>16</v>
       </c>
       <c r="B12" s="1">
         <v>46093</v>
       </c>
-      <c r="D12" t="s">
+      <c r="C12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="1">
         <v>46093</v>
       </c>
-      <c r="D13" t="s">
+      <c r="C13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -589,7 +595,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -600,31 +606,53 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="1">
         <v>46097</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="1">
         <v>46097</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>46093</v>
       </c>
-      <c r="D18" t="s">
+      <c r="C18" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46100</v>
       </c>
     </row>
   </sheetData>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29810" yWindow="660" windowWidth="12010" windowHeight="13630" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,12 +16,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -687,7 +693,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Allegato con DDT (19/03/2026)</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
@@ -859,52 +865,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p2389</t>
+          <t>p13590</t>
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>p13590</t>
+          <t>p2001</t>
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>p6032</t>
+          <t>p2384</t>
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>p2001</t>
+          <t>p2655</t>
         </is>
       </c>
       <c r="B33" s="1" t="n">
@@ -912,14 +918,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>p2384</t>
+          <t>p11826</t>
         </is>
       </c>
       <c r="B34" s="1" t="n">
@@ -927,14 +933,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>p2108</t>
+          <t>p1895</t>
         </is>
       </c>
       <c r="B35" s="1" t="n">
@@ -942,84 +948,89 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>p2655</t>
+          <t>p1895</t>
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 26-03-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>p11826</t>
+          <t>p2240</t>
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>p8840</t>
+          <t>p1811</t>
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>p1895</t>
+          <t>p2243</t>
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>p1895</t>
+          <t>p1807</t>
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46099</v>
+        <v>46107</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>p2240</t>
+          <t>p2244</t>
         </is>
       </c>
       <c r="B41" s="1" t="n">
@@ -1027,14 +1038,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>p1811</t>
+          <t>p1810</t>
         </is>
       </c>
       <c r="B42" s="1" t="n">
@@ -1042,14 +1053,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>p2243</t>
+          <t>p8992</t>
         </is>
       </c>
       <c r="B43" s="1" t="n">
@@ -1057,14 +1068,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>p1807</t>
+          <t>p2023</t>
         </is>
       </c>
       <c r="B44" s="1" t="n">
@@ -1072,67 +1083,67 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>p2244</t>
+          <t>p2389</t>
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>p1810</t>
+          <t>p6032</t>
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>p8992</t>
+          <t>p8840</t>
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>p2023</t>
+          <t>p2108</t>
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2026</t>
+          <t>allegato DDT 30-03-2026_31-03-2026</t>
         </is>
       </c>
     </row>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29810" yWindow="660" windowWidth="12010" windowHeight="13630" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29810" yWindow="50" windowWidth="12010" windowHeight="13630" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,18 +16,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
   </fonts>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -3,12 +3,14 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="29810" yWindow="50" windowWidth="12010" windowHeight="13630" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rientri'!$A$1:$C$1</definedName>
+  </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -1142,6 +1144,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C13334E-BC88-40D7-9257-000A21ADFDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9BCFF7-2340-4D3F-BEF6-72DA75AE65D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38070" yWindow="40" windowWidth="12010" windowHeight="13630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" r:id="rId1"/>
@@ -94,9 +94,6 @@
     <t>p2023</t>
   </si>
   <si>
-    <t>allegato DDT 30-03-2026_31-03-2026</t>
-  </si>
-  <si>
     <t>p2359</t>
   </si>
   <si>
@@ -152,6 +149,9 @@
   </si>
   <si>
     <t>p2240</t>
+  </si>
+  <si>
+    <t>In lavorazione</t>
   </si>
   <si>
     <t>p1811</t>
@@ -729,211 +729,211 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="1">
         <v>46100</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1">
         <v>46100</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1">
         <v>46100</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1">
         <v>46100</v>
       </c>
       <c r="C22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B23" s="1">
         <v>46100</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B24" s="1">
         <v>46100</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B25" s="1">
         <v>46100</v>
       </c>
       <c r="C25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1">
         <v>46100</v>
       </c>
       <c r="C26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1">
         <v>46100</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B28" s="1">
         <v>46100</v>
       </c>
       <c r="C28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="1">
         <v>46104</v>
       </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1">
         <v>46107</v>
       </c>
       <c r="C30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1">
         <v>46106</v>
       </c>
       <c r="C31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1">
         <v>46105</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="1">
         <v>46106</v>
       </c>
       <c r="C33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1">
         <v>46105</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="1">
         <v>46106</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="1">
         <v>46099</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" s="1">
         <v>46107</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
@@ -944,7 +944,7 @@
         <v>46107</v>
       </c>
       <c r="C38" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
@@ -955,7 +955,7 @@
         <v>46107</v>
       </c>
       <c r="C39" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
@@ -966,7 +966,7 @@
         <v>46107</v>
       </c>
       <c r="C40" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -977,7 +977,7 @@
         <v>46107</v>
       </c>
       <c r="C41" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -988,7 +988,7 @@
         <v>46107</v>
       </c>
       <c r="C42" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
@@ -999,7 +999,7 @@
         <v>46107</v>
       </c>
       <c r="C43" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -1010,7 +1010,7 @@
         <v>46107</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
@@ -1021,7 +1021,7 @@
         <v>46106</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
@@ -1032,7 +1032,7 @@
         <v>46106</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
@@ -1043,7 +1043,7 @@
         <v>46106</v>
       </c>
       <c r="C47" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
@@ -1054,7 +1054,7 @@
         <v>46106</v>
       </c>
       <c r="C48" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C9BCFF7-2340-4D3F-BEF6-72DA75AE65D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA9BE23-C199-4849-8278-CA2ACDEC64C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38070" yWindow="40" windowWidth="12010" windowHeight="13630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
   <si>
     <t>Codice consegna</t>
   </si>
@@ -151,9 +151,6 @@
     <t>p2240</t>
   </si>
   <si>
-    <t>In lavorazione</t>
-  </si>
-  <si>
     <t>p1811</t>
   </si>
   <si>
@@ -182,16 +179,58 @@
   </si>
   <si>
     <t>p2108</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2026</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2027</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2028</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2029</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2030</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2031</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2032</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2033</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2034</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2035</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2036</t>
+  </si>
+  <si>
+    <t>allegato DDT 30-03-2027_31-03-2037</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -933,73 +972,73 @@
         <v>46107</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B38" s="1">
         <v>46107</v>
       </c>
       <c r="C38" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B39" s="1">
         <v>46107</v>
       </c>
       <c r="C39" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B40" s="1">
         <v>46107</v>
       </c>
       <c r="C40" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" s="1">
         <v>46107</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="1">
         <v>46107</v>
       </c>
       <c r="C42" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B43" s="1">
         <v>46107</v>
       </c>
       <c r="C43" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
@@ -1010,55 +1049,56 @@
         <v>46107</v>
       </c>
       <c r="C44" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B45" s="1">
         <v>46106</v>
       </c>
       <c r="C45" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" s="1">
         <v>46106</v>
       </c>
       <c r="C46" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" s="1">
         <v>46106</v>
       </c>
       <c r="C47" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B48" s="1">
         <v>46106</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA9BE23-C199-4849-8278-CA2ACDEC64C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42500EAC-F9D3-405C-B8F8-E161058D3536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38070" yWindow="40" windowWidth="12010" windowHeight="13630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Codice consegna</t>
   </si>
@@ -561,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr defaultColWidth="20.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
@@ -1096,6 +1096,62 @@
         <v>63</v>
       </c>
     </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>40</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46106</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\AppLogSolution\dati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42500EAC-F9D3-405C-B8F8-E161058D3536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37DE5265-2485-40AE-B64E-AC85D1495854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27300" yWindow="680" windowWidth="18990" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rientri" sheetId="1" r:id="rId1"/>
+    <sheet name="Foglio2" sheetId="3" r:id="rId2"/>
+    <sheet name="Foglio1" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Rientri!$A$1:$C$1</definedName>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="65">
   <si>
     <t>Codice consegna</t>
   </si>
@@ -88,6 +90,9 @@
     <t>p2381</t>
   </si>
   <si>
+    <t>allegato DDT 13-04-2026</t>
+  </si>
+  <si>
     <t>p2673</t>
   </si>
   <si>
@@ -127,12 +132,12 @@
     <t>p2022</t>
   </si>
   <si>
+    <t>p13590</t>
+  </si>
+  <si>
     <t>allegato DDT 26-03-2026</t>
   </si>
   <si>
-    <t>p13590</t>
-  </si>
-  <si>
     <t>p2001</t>
   </si>
   <si>
@@ -151,86 +156,80 @@
     <t>p2240</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2026</t>
+  </si>
+  <si>
     <t>p1811</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2027</t>
+  </si>
+  <si>
     <t>p2243</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2028</t>
+  </si>
+  <si>
     <t>p1807</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2029</t>
+  </si>
+  <si>
     <t>p2244</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2030</t>
+  </si>
+  <si>
     <t>p1810</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2031</t>
+  </si>
+  <si>
     <t>p8992</t>
   </si>
   <si>
     <t>p2389</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2034</t>
+  </si>
+  <si>
     <t>p6032</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2035</t>
+  </si>
+  <si>
     <t>p8840</t>
   </si>
   <si>
+    <t>allegato DDT 30-03-2027_31-03-2036</t>
+  </si>
+  <si>
     <t>p2108</t>
   </si>
   <si>
-    <t>allegato DDT 30-03-2027_31-03-2026</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2027</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2028</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2029</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2030</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2031</t>
+    <t>allegato DDT 30-03-2027_31-03-2037</t>
   </si>
   <si>
     <t>allegato DDT 30-03-2027_31-03-2032</t>
   </si>
   <si>
     <t>allegato DDT 30-03-2027_31-03-2033</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2034</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2035</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2036</t>
-  </si>
-  <si>
-    <t>allegato DDT 30-03-2027_31-03-2037</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -561,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultColWidth="20.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
@@ -741,23 +740,23 @@
         <v>46097</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1">
         <v>46097</v>
       </c>
       <c r="C17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1">
         <v>46093</v>
@@ -768,123 +767,123 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1">
         <v>46100</v>
       </c>
       <c r="C19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C20" t="s">
         <v>25</v>
-      </c>
-      <c r="B20" s="1">
-        <v>46100</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1">
         <v>46100</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C22" t="s">
         <v>28</v>
-      </c>
-      <c r="B22" s="1">
-        <v>46100</v>
-      </c>
-      <c r="C22" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23" s="1">
         <v>46100</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1">
         <v>46100</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1">
         <v>46100</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1">
         <v>46100</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1">
         <v>46100</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1">
         <v>46100</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1">
         <v>46104</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
@@ -895,266 +894,1517 @@
         <v>46107</v>
       </c>
       <c r="C30" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C31" t="s">
         <v>36</v>
-      </c>
-      <c r="B31" s="1">
-        <v>46106</v>
-      </c>
-      <c r="C31" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1">
         <v>46105</v>
       </c>
       <c r="C32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1">
         <v>46106</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1">
         <v>46105</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1">
         <v>46106</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B36" s="1">
         <v>46099</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B37" s="1">
         <v>46107</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1">
         <v>46107</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1">
         <v>46107</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B40" s="1">
         <v>46107</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B41" s="1">
         <v>46107</v>
       </c>
       <c r="C41" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B42" s="1">
         <v>46107</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B43" s="1">
         <v>46107</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B44" s="1">
         <v>46107</v>
       </c>
       <c r="C44" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B45" s="1">
         <v>46106</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B46" s="1">
         <v>46106</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B47" s="1">
         <v>46106</v>
       </c>
       <c r="C47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1">
         <v>46106</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B49" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B50" s="1">
         <v>46106</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B51" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B52" s="1">
         <v>46106</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B53" s="1">
         <v>46099</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B54" s="1">
         <v>46106</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1">
         <v>46106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46107</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D169B030-0950-4E11-8812-3BBA84F8BB88}">
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C57"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="22.36328125" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46086</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46091</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46092</v>
+      </c>
+      <c r="C14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46085</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46097</v>
+      </c>
+      <c r="C17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46093</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46105</v>
+      </c>
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46099</v>
+      </c>
+      <c r="C36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C37" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C40" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C42" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C43" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46107</v>
+      </c>
+      <c r="C44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C45" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C51" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46106</v>
+      </c>
+      <c r="C54" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>23</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>54</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46107</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1167,7 +1167,11 @@
       <c r="B50" s="1" t="n">
         <v>46106</v>
       </c>
-      <c r="C50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>in lavorazione</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1193,7 +1197,11 @@
       <c r="B52" s="1" t="n">
         <v>46106</v>
       </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>allegato DDT 15-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1204,7 +1212,11 @@
       <c r="B53" s="1" t="n">
         <v>46099</v>
       </c>
-      <c r="C53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>allegato DDT 15-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1215,7 +1227,11 @@
       <c r="B54" s="1" t="n">
         <v>46106</v>
       </c>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>allegato DDT 15-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="26990" yWindow="300" windowWidth="18990" windowHeight="12750" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>in lavorazione</t>
+          <t>allegato DDT 15-04-2026</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>allegato DDT 15-04-2026</t>
+          <t>allegato DDT 30-03-2027_31-03-2037</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>allegato DDT 30-03-2027_31-03-2037</t>
+          <t>allegato DDT 15-04-2026</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,11 @@
       <c r="B56" s="1" t="n">
         <v>46107</v>
       </c>
-      <c r="C56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>allegato DDT 16-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1268,7 +1272,11 @@
       <c r="B57" s="1" t="n">
         <v>46107</v>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>allegato DDT 16-04-2026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="26990" yWindow="300" windowWidth="18990" windowHeight="12750" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1278,6 +1278,61 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>p2655</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="C58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>p2108</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="C59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>p2120</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="C60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>p2328</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>p1851</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="C62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dati/rientri_ddt.xlsx
+++ b/dati/rientri_ddt.xlsx
@@ -1287,7 +1287,11 @@
       <c r="B58" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>allegato DDT 22-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1298,7 +1302,11 @@
       <c r="B59" s="1" t="n">
         <v>46106</v>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>allegato DDT 22-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1309,7 +1317,11 @@
       <c r="B60" s="1" t="n">
         <v>46127</v>
       </c>
-      <c r="C60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>allegato DDT 22-04-2026</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
